--- a/ci-cd-merge-resolver/repoCollector/datasets/streamex.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/streamex.xlsx
@@ -80,6 +80,18 @@
     <t>adbaa5c742b4532a81117f20a15e4b1d70d14c03</t>
   </si>
   <si>
+    <t>dae981a4955899f007f362544af1ebc6fb11dd99</t>
+  </si>
+  <si>
+    <t>89c1668a5de8642b0a319896bf8038701e06e0d2</t>
+  </si>
+  <si>
+    <t>a3926a3b3161477eae70da3672a2ed78978c779d</t>
+  </si>
+  <si>
+    <t>c7c7ae7dcfcc34e55857c9168ff2037b6c324325</t>
+  </si>
+  <si>
     <t>74cf4df672fe1a474d8f48f9797b8cb8e06d2083</t>
   </si>
   <si>
@@ -87,18 +99,6 @@
   </si>
   <si>
     <t>49e46f9a106f0a26e5e11b74aacb15a9a8e6dbaf</t>
-  </si>
-  <si>
-    <t>89c1668a5de8642b0a319896bf8038701e06e0d2</t>
-  </si>
-  <si>
-    <t>a3926a3b3161477eae70da3672a2ed78978c779d</t>
-  </si>
-  <si>
-    <t>c7c7ae7dcfcc34e55857c9168ff2037b6c324325</t>
-  </si>
-  <si>
-    <t>dae981a4955899f007f362544af1ebc6fb11dd99</t>
   </si>
   <si>
     <t>f417363a6b21dac4cce7c28cb89063c7f0204c9a</t>
@@ -207,13 +207,13 @@
         <v>2.0</v>
       </c>
       <c r="G2" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="b" s="0">
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>1.4950000047683716</v>
+        <v>2.557000160217285</v>
       </c>
       <c r="J2" t="b" s="0">
         <v>0</v>
@@ -239,13 +239,13 @@
         <v>1.0</v>
       </c>
       <c r="G3" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="b" s="0">
         <v>1</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>3.2659997940063477</v>
+        <v>2.547999858856201</v>
       </c>
       <c r="J3" t="b" s="0">
         <v>0</v>
@@ -262,7 +262,7 @@
         <v>18</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>447.0</v>
+        <v>452.0</v>
       </c>
       <c r="E4" t="n" s="0">
         <v>4.0</v>
@@ -277,7 +277,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>16.727998733520508</v>
+        <v>15.45099925994873</v>
       </c>
       <c r="J4" t="b" s="0">
         <v>0</v>
@@ -303,13 +303,13 @@
         <v>1.0</v>
       </c>
       <c r="G5" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="b" s="0">
         <v>1</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>18.0310001373291</v>
+        <v>16.010000228881836</v>
       </c>
       <c r="J5" t="b" s="0">
         <v>0</v>
@@ -320,28 +320,28 @@
         <v>22</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>478.0</v>
+        <v>452.0</v>
       </c>
       <c r="E6" t="n" s="0">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="F6" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G6" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="b" s="0">
         <v>1</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>18.451000213623047</v>
+        <v>16.678998947143555</v>
       </c>
       <c r="J6" t="b" s="0">
         <v>0</v>
@@ -349,13 +349,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s" s="0">
         <v>25</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s" s="0">
-        <v>27</v>
       </c>
       <c r="D7" t="n" s="0">
         <v>454.0</v>
@@ -367,13 +367,13 @@
         <v>1.0</v>
       </c>
       <c r="G7" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="b" s="0">
         <v>1</v>
       </c>
       <c r="I7" t="n" s="0">
-        <v>17.12900161743164</v>
+        <v>16.387001037597656</v>
       </c>
       <c r="J7" t="b" s="0">
         <v>0</v>
@@ -381,31 +381,31 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="B8" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="C8" t="s" s="0">
-        <v>18</v>
-      </c>
       <c r="D8" t="n" s="0">
-        <v>452.0</v>
+        <v>478.0</v>
       </c>
       <c r="E8" t="n" s="0">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="F8" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G8" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="b" s="0">
         <v>1</v>
       </c>
       <c r="I8" t="n" s="0">
-        <v>16.35000228881836</v>
+        <v>15.717000961303711</v>
       </c>
       <c r="J8" t="b" s="0">
         <v>0</v>
@@ -431,13 +431,13 @@
         <v>7.0</v>
       </c>
       <c r="G9" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="b" s="0">
         <v>1</v>
       </c>
       <c r="I9" t="n" s="0">
-        <v>16.32900047302246</v>
+        <v>15.03000259399414</v>
       </c>
       <c r="J9" t="b" s="0">
         <v>0</v>
